--- a/backend/Backend-Daily-Tracker.xlsx
+++ b/backend/Backend-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="90">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -478,6 +478,12 @@
   </si>
   <si>
     <t>Tested the new system after the whole update for security flaws, logged in account issues. Found that reviews were not linked to the businesses yet</t>
+  </si>
+  <si>
+    <t>Fixed the stale admin session issue on page load and added role-based login redirects, so admins and regular users land on the correct pages after signing in. Updated the admin navbar and logout so logging out now takes the user to the login page. Improved admin session security by making sessions end when the browser closes and shortening the admin token lifetime to 8 hours. Added a script to import WordPress reviews into the platform. Updated the zustand dependency to version 4.5.7 and refreshed the generated Next.js type file. Investigated why the admin-managed hero images were not appearing on the homepage. The cause was server-side caching combined with a missing browser refetch, and I fixed it so the homepage now shows the latest hero images. Also fixed the disabled "Email announcement" button on the Customers page, which stayed greyed out for owners with a single business. Finalized the project structure and updated .gitignore so that environment files, uploads, and private user data are not pushed to GitHub.</t>
+  </si>
+  <si>
+    <t>1. Fix stale admin session on load; role-based login redirect; admin navbar and logout to /login           2. Admin sessions end when the browser closes; 8h admin token                 3. Add WordPress review import script Bump zustand to 4.5.7 and update generated next-env.d.ts                           5. Fix hero images not refreshing and enable email announcement for single-business owners      6. fix: finalized project changes and hidden private datas                     7. docs: added daily tracker spreadsheet</t>
   </si>
 </sst>
 </file>
@@ -1997,18 +2003,26 @@
       </c>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="277.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>34</v>
       </c>
-      <c r="B38" s="3"/>
+      <c r="B38" s="5">
+        <v>46301</v>
+      </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="3"/>
+      <c r="D38" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="E38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="H38" s="3"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Daily-Tracker.xlsx
+++ b/backend/Backend-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -484,6 +484,12 @@
   </si>
   <si>
     <t>1. Fix stale admin session on load; role-based login redirect; admin navbar and logout to /login           2. Admin sessions end when the browser closes; 8h admin token                 3. Add WordPress review import script Bump zustand to 4.5.7 and update generated next-env.d.ts                           5. Fix hero images not refreshing and enable email announcement for single-business owners      6. fix: finalized project changes and hidden private datas                     7. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tested the ijnternal features and potentail security issues </t>
+  </si>
+  <si>
+    <t>4 hours</t>
   </si>
 </sst>
 </file>
@@ -2025,18 +2031,26 @@
       </c>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>35</v>
       </c>
-      <c r="B39" s="3"/>
+      <c r="B39" s="5">
+        <v>46302</v>
+      </c>
       <c r="C39" s="2"/>
-      <c r="D39" s="3"/>
+      <c r="D39" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="E39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="H39" s="3"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Daily-Tracker.xlsx
+++ b/backend/Backend-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="94">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -490,6 +490,52 @@
   </si>
   <si>
     <t>4 hours</t>
+  </si>
+  <si>
+    <r>
+      <t>Rewrote the project README files (root, frontend and backend) to replace the starter-template text with accurate setup steps, environment variables and folder structure. Created a full backup of the PostgreSQL database (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>autohub_full.dmp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) from the Docker container and tested the restore on a separate database, confirming the data matched (36 users, 40 businesses, 11 reviews). Wrote a separate </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>DATABASE_RESTORE.md</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> guide explaining how to restore the dump and connect the backend.</t>
+    </r>
+  </si>
+  <si>
+    <t>1. docs: rewrite root, frontend and backend README files                               2. docs: added daily tracker spreadsheet</t>
   </si>
 </sst>
 </file>
@@ -2053,18 +2099,26 @@
       </c>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="145.19999999999999" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>36</v>
       </c>
-      <c r="B40" s="3"/>
+      <c r="B40" s="5">
+        <v>46303</v>
+      </c>
       <c r="C40" s="2"/>
-      <c r="D40" s="3"/>
+      <c r="D40" s="11" t="s">
+        <v>92</v>
+      </c>
       <c r="E40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Daily-Tracker.xlsx
+++ b/backend/Backend-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="97">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -536,6 +536,55 @@
   </si>
   <si>
     <t>1. docs: rewrite root, frontend and backend README files                               2. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <r>
+      <t>Tested the platform end to end on a public domain using Cloudflare Tunnel, to check that image uploads, admin login and API requests work outside localhost. Set up tunnels for the frontend and backend, configured the environment variables (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>NEXT_PUBLIC_API_URL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>FRONTEND_URL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) and verified the API through the public address. Diagnosed and fixed several issues that appeared on the live domain:</t>
+    </r>
+  </si>
+  <si>
+    <t>6 hours</t>
+  </si>
+  <si>
+    <t>1. chore: add optional NEXT_IMAGE_UNOPTIMIZED toggle for tunnel testing                               2. docs: added daily tracker spreadsheet</t>
   </si>
 </sst>
 </file>
@@ -2121,20 +2170,26 @@
       </c>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="130.19999999999999" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>37</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41" s="3"/>
+      <c r="B41" s="5">
+        <v>46304</v>
+      </c>
+      <c r="C41" s="12"/>
+      <c r="D41" s="11" t="s">
+        <v>94</v>
+      </c>
       <c r="E41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="H41" s="3"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
@@ -2142,7 +2197,9 @@
         <v>38</v>
       </c>
       <c r="B42" s="3"/>
-      <c r="C42" s="2"/>
+      <c r="C42" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="D42" s="3"/>
       <c r="E42" s="2" t="s">
         <v>10</v>

--- a/backend/Backend-Daily-Tracker.xlsx
+++ b/backend/Backend-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="99">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -585,6 +585,12 @@
   </si>
   <si>
     <t>1. chore: add optional NEXT_IMAGE_UNOPTIMIZED toggle for tunnel testing                               2. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t>1. feat(security): add audit log, login lockout, session revocation and stricter password rules                      2. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t>Added an AuditLog table recording who did what and when: logins and failed logins, admin approvals, role changes, user deletions, hero image and popup ad changes, and announcements sent.</t>
   </si>
 </sst>
 </file>
@@ -2192,20 +2198,26 @@
       </c>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>38</v>
       </c>
-      <c r="B42" s="3"/>
+      <c r="B42" s="5">
+        <v>46308</v>
+      </c>
       <c r="C42" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D42" s="3"/>
+      <c r="D42" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="E42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F42" s="2"/>
-      <c r="G42" s="3"/>
+      <c r="G42" s="11" t="s">
+        <v>97</v>
+      </c>
       <c r="H42" s="3"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Daily-Tracker.xlsx
+++ b/backend/Backend-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="101">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -591,6 +591,12 @@
   </si>
   <si>
     <t>Added an AuditLog table recording who did what and when: logins and failed logins, admin approvals, role changes, user deletions, hero image and popup ad changes, and announcements sent.</t>
+  </si>
+  <si>
+    <t>Started the frontend for the audit log page for  admin view</t>
+  </si>
+  <si>
+    <t>10 hours</t>
   </si>
 </sst>
 </file>
@@ -2212,26 +2218,36 @@
         <v>98</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="G42" s="11" t="s">
         <v>97</v>
       </c>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>39</v>
       </c>
-      <c r="B43" s="3"/>
+      <c r="B43" s="5">
+        <v>46309</v>
+      </c>
       <c r="C43" s="2"/>
-      <c r="D43" s="3"/>
+      <c r="D43" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="E43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="H43" s="3"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Daily-Tracker.xlsx
+++ b/backend/Backend-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="104">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -597,6 +597,36 @@
   </si>
   <si>
     <t>10 hours</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Added a security update to the backend and admin panel. On the backend: an audit log that records sign-ins, failed attempts, password resets and admin actions; stronger password rules that match the frontend; a temporary account lockout after repeated failed logins; and “log out everywhere”, which invalidates old sessions after a password reset. The server also now refuses to start without a valid </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>JWT_SECRET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. On the frontend, I built an admin Audit log page with filters, pagination and expandable details, plus unit tests for its labels.</t>
+    </r>
+  </si>
+  <si>
+    <t>11 hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. feat(security): add audit log, login lockout, session revocation and stricter password rules                    2. feat(admin): add audit log page                                  3. docs: added daily tracker spreadsheet                     </t>
   </si>
 </sst>
 </file>
@@ -2243,25 +2273,33 @@
         <v>20</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="159" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>40</v>
       </c>
-      <c r="B44" s="3"/>
+      <c r="B44" s="5">
+        <v>46310</v>
+      </c>
       <c r="C44" s="2"/>
-      <c r="D44" s="3"/>
+      <c r="D44" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="E44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="H44" s="3"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Daily-Tracker.xlsx
+++ b/backend/Backend-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="105">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>Week 1</t>
-  </si>
-  <si>
-    <t>Todo</t>
   </si>
   <si>
     <t>Week 2</t>
@@ -599,34 +596,19 @@
     <t>10 hours</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Added a security update to the backend and admin panel. On the backend: an audit log that records sign-ins, failed attempts, password resets and admin actions; stronger password rules that match the frontend; a temporary account lockout after repeated failed logins; and “log out everywhere”, which invalidates old sessions after a password reset. The server also now refuses to start without a valid </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>JWT_SECRET</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. On the frontend, I built an admin Audit log page with filters, pagination and expandable details, plus unit tests for its labels.</t>
-    </r>
-  </si>
-  <si>
     <t>11 hours</t>
   </si>
   <si>
     <t xml:space="preserve">1. feat(security): add audit log, login lockout, session revocation and stricter password rules                    2. feat(admin): add audit log page                                  3. docs: added daily tracker spreadsheet                     </t>
+  </si>
+  <si>
+    <t>Added a security update to the backend and admin panel. On the backend: an audit log that records sign-ins, failed attempts, password resets and admin actions; stronger password rules that match the frontend; a temporary account lockout after repeated failed logins; and “log out everywhere”, which invalidates old sessions after a password reset. The server also now refuses to start without a valid JWT_SECRET. On the frontend, I built an admin Audit log page with filters, pagination and expandable details, plus unit tests for its labels.</t>
+  </si>
+  <si>
+    <t>Built email verification at signup. New accounts now confirm their email before they can log in, with a resend option on the frontend. This also fixes two account-takeover gaps: an unconfirmed account is now secured when its owner signs in with Google or Facebook, or resets the password. Added a Content Security Policy for the API and a rollout-safe one for the website, plus security headers. Added a “Sign out of all devices” button to the dashboard. Built optional analytics (Google Analytics 4 or Plausible) that only starts after the cookie “Accept” and respects Do Not Track, with unit tests. Set up production deployment with Docker and automatic HTTPS, backup and restore scripts, and .env.example files. Built a CI/CD pipeline in GitHub Actions: checks on every change, including a database migration test, then image builds, an approval-gated deploy with automatic rollback, a manual roll-back workflow, and Dependabot. Wrote deployment, CI/CD and security docs, and updated the READMEs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. feat(auth): add email verification, close pre-registration takeover, lock down API CSP                             2. feat(web): email verification screens, sign out everywhere, consent-gated analytics, security headers                                       3. chore(ops): add Docker deployment, backup scripts, CI and security docs                                         4. docs: added daily tracker spreadsheet    </t>
   </si>
 </sst>
 </file>
@@ -731,7 +713,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -772,6 +754,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1333,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1348,7 +1333,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -1407,13 +1392,13 @@
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="6"/>
@@ -1427,19 +1412,19 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
@@ -1451,16 +1436,16 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H7" s="6"/>
     </row>
@@ -1473,19 +1458,19 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="66" x14ac:dyDescent="0.3">
@@ -1497,16 +1482,16 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="H9" s="3"/>
     </row>
@@ -1515,22 +1500,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="H10" s="3"/>
     </row>
@@ -1543,19 +1528,19 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
@@ -1567,16 +1552,16 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="H12" s="3"/>
     </row>
@@ -1589,16 +1574,16 @@
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="H13" s="3"/>
     </row>
@@ -1611,16 +1596,16 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="H14" s="3"/>
     </row>
@@ -1632,19 +1617,19 @@
         <v>46272</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="H15" s="3"/>
     </row>
@@ -1657,16 +1642,16 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H16" s="3"/>
     </row>
@@ -1679,16 +1664,16 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H17" s="3"/>
     </row>
@@ -1701,16 +1686,16 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H18" s="3"/>
     </row>
@@ -1723,19 +1708,19 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="66" x14ac:dyDescent="0.3">
@@ -1746,22 +1731,22 @@
         <v>46279</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
@@ -1773,16 +1758,16 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="H21" s="3"/>
     </row>
@@ -1795,16 +1780,16 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H22" s="3"/>
     </row>
@@ -1817,16 +1802,16 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="H23" s="3"/>
     </row>
@@ -1839,16 +1824,16 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="10" t="s">
         <v>63</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>64</v>
       </c>
       <c r="H24" s="3"/>
     </row>
@@ -1860,19 +1845,19 @@
         <v>46286</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="H25" s="3"/>
     </row>
@@ -1885,16 +1870,16 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="H26" s="3"/>
     </row>
@@ -1907,16 +1892,16 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="H27" s="3"/>
     </row>
@@ -1929,16 +1914,16 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="H28" s="3"/>
     </row>
@@ -1951,16 +1936,16 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="H29" s="3"/>
     </row>
@@ -1973,16 +1958,16 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H30" s="3"/>
     </row>
@@ -1994,19 +1979,19 @@
         <v>46293</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D31" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="H31" s="3"/>
     </row>
@@ -2019,16 +2004,16 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -2043,16 +2028,16 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="H33" s="3"/>
     </row>
@@ -2065,16 +2050,16 @@
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H34" s="3"/>
     </row>
@@ -2087,16 +2072,16 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H35" s="3"/>
     </row>
@@ -2108,19 +2093,19 @@
         <v>46299</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D36" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="H36" s="3"/>
     </row>
@@ -2133,16 +2118,16 @@
       </c>
       <c r="C37" s="12"/>
       <c r="D37" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H37" s="3"/>
     </row>
@@ -2155,16 +2140,16 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="H38" s="3"/>
     </row>
@@ -2177,16 +2162,16 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="G39" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H39" s="3"/>
     </row>
@@ -2199,16 +2184,16 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="H40" s="3"/>
     </row>
@@ -2221,16 +2206,16 @@
       </c>
       <c r="C41" s="12"/>
       <c r="D41" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F41" s="2" t="s">
+      <c r="G41" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="H41" s="3"/>
     </row>
@@ -2242,19 +2227,19 @@
         <v>46308</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H42" s="3"/>
     </row>
@@ -2267,20 +2252,20 @@
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:8" ht="159" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="145.19999999999999" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>40</v>
       </c>
@@ -2288,33 +2273,44 @@
         <v>46310</v>
       </c>
       <c r="C44" s="2"/>
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="264" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>41</v>
       </c>
-      <c r="B45" s="3"/>
+      <c r="B45" s="5">
+        <v>46311</v>
+      </c>
       <c r="C45" s="2"/>
-      <c r="D45" s="3"/>
+      <c r="D45" s="6" t="s">
+        <v>103</v>
+      </c>
       <c r="E45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="H45" s="3"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G47" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/backend/Backend-Daily-Tracker.xlsx
+++ b/backend/Backend-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="108">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -609,6 +609,15 @@
   </si>
   <si>
     <t xml:space="preserve">1. feat(auth): add email verification, close pre-registration takeover, lock down API CSP                             2. feat(web): email verification screens, sign out everywhere, consent-gated analytics, security headers                                       3. chore(ops): add Docker deployment, backup scripts, CI and security docs                                         4. docs: added daily tracker spreadsheet    </t>
+  </si>
+  <si>
+    <t>Week 9</t>
+  </si>
+  <si>
+    <t>1. feat(owner): add error boundary, not-found page and orders error state                   2. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t>Added error handling to the owner dashboard. Built a shared QueryError card with a Try again button, an owner error.tsx error boundary, and a “Page not found” page for unknown owner URLs. On the Orders page Replaced the plain “Couldn’t load orders.” text with the new error card, and Replaced an as any with the existing getErrorMessage helper. Set up the project locally (dependencies, Docker database, Prisma schema and seed data) and moved the work onto a new branch from customer-redesign, because can’t merge to main right now. ran ESLint on the changed files with no errors, and then tested in the browser. An unknown owner URL showed the not-found card inside the dashboard. With the API stopped, Orders showed the error card, and Try again loaded the orders once the API was back</t>
   </si>
 </sst>
 </file>
@@ -686,7 +695,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -709,11 +718,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -751,17 +773,111 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="48">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1318,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1332,28 +1448,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="4" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2288,29 +2404,110 @@
       <c r="H44" s="3"/>
     </row>
     <row r="45" spans="1:8" ht="264" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
+      <c r="A45" s="17">
         <v>41</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="18">
         <v>46311</v>
       </c>
-      <c r="C45" s="2"/>
+      <c r="C45" s="17"/>
       <c r="D45" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F45" s="2" t="s">
+      <c r="E45" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="H45" s="3"/>
+      <c r="H45" s="19"/>
+    </row>
+    <row r="46" spans="1:8" ht="211.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>42</v>
+      </c>
+      <c r="B46" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="H46" s="3"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G47" s="16"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="20"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="20"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="20"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="20"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="20"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2318,133 +2515,147 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E29 E42:E44 E37:E39 E33:E34">
-    <cfRule type="cellIs" dxfId="35" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="41" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="42" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="43" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="44" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="cellIs" dxfId="31" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="37" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="38" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="39" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="40" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="27" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="33" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="34" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="35" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="36" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="29" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="30" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="31" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="32" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E36">
-    <cfRule type="cellIs" dxfId="19" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="25" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="26" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="27" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="28" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35">
-    <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="21" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="22" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="23" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="24" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="13" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="14" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="15" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="16" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="10" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+      <formula>"Complete"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E46">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+      <formula>"Todo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E5:E45">
+    <dataValidation type="list" sqref="E5:E46">
       <formula1>"Todo,In Progress,Blocked,Complete"</formula1>
     </dataValidation>
   </dataValidations>

--- a/backend/Backend-Daily-Tracker.xlsx
+++ b/backend/Backend-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="112">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -618,6 +618,20 @@
   </si>
   <si>
     <t>Added error handling to the owner dashboard. Built a shared QueryError card with a Try again button, an owner error.tsx error boundary, and a “Page not found” page for unknown owner URLs. On the Orders page Replaced the plain “Couldn’t load orders.” text with the new error card, and Replaced an as any with the existing getErrorMessage helper. Set up the project locally (dependencies, Docker database, Prisma schema and seed data) and moved the work onto a new branch from customer-redesign, because can’t merge to main right now. ran ESLint on the changed files with no errors, and then tested in the browser. An unknown owner URL showed the not-found card inside the dashboard. With the API stopped, Orders showed the error card, and Try again loaded the orders once the API was back</t>
+  </si>
+  <si>
+    <t>Added the chatbot backend for the restaurant platform. This includes new ChatSession and ChatMessage database models, and a chats module with a keyword-based bot that answers from real restaurant data (menu, offers, address, payment methods) in English and Japanese. It also has an optional AI fallback through Groq for questions the rules don’t cover, owner and platform-admin reply and close routes, and a visitor polling endpoint, with owner access limited to chats in their own tenant. I tested it end to end in Swagger: starting a chat, the bot replies, thread polling, and tenant isolation, which returned no chats for an owner from a different restaurant. The AI fallback first failed because Groq had retired the default model, so I updated the default model in the service. The server compiles cleanly, and the work is committed and pushed to the chatbot-backend branch.</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. feat(chats): add chat models
+2. feat(chats): add chats module
+3. fix(chats): update default groq model                              4. docs: added daily tracker spreadsheet                     </t>
+  </si>
+  <si>
+    <t>Owner reply and takeover, closing a chat, platform-admin routes and the frontend widget are still to be tested or built. Pranav needs to be told about the shared-schema change before the PR is merged.</t>
   </si>
 </sst>
 </file>
@@ -735,7 +749,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -773,12 +787,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -789,39 +797,14 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="48">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD1FAE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDBEAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F4F6"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="44">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1448,28 +1431,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="4" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2404,26 +2387,26 @@
       <c r="H44" s="3"/>
     </row>
     <row r="45" spans="1:8" ht="264" x14ac:dyDescent="0.3">
-      <c r="A45" s="17">
+      <c r="A45" s="13">
         <v>41</v>
       </c>
-      <c r="B45" s="18">
+      <c r="B45" s="14">
         <v>46311</v>
       </c>
-      <c r="C45" s="17"/>
+      <c r="C45" s="13"/>
       <c r="D45" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E45" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F45" s="17" t="s">
+      <c r="E45" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="G45" s="19" t="s">
+      <c r="G45" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="H45" s="19"/>
+      <c r="H45" s="15"/>
     </row>
     <row r="46" spans="1:8" ht="211.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
@@ -2449,65 +2432,79 @@
       </c>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="20"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="20"/>
+    <row r="47" spans="1:8" ht="224.4" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>43</v>
+      </c>
+      <c r="B47" s="5">
+        <v>46322</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="20"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
+      <c r="A49" s="16"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="20"/>
-      <c r="B50" s="20"/>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
+      <c r="A50" s="16"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="20"/>
-      <c r="B51" s="20"/>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
+      <c r="A51" s="16"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="20"/>
-      <c r="B52" s="20"/>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
+      <c r="A52" s="16"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2515,147 +2512,161 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E29 E42:E44 E37:E39 E33:E34">
-    <cfRule type="cellIs" dxfId="47" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="45" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="46" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="47" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="48" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="cellIs" dxfId="43" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="41" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="42" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="43" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="44" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="39" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="37" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="38" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="39" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="40" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="35" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="33" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="34" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="35" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="36" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E36">
-    <cfRule type="cellIs" dxfId="31" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="29" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="30" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="31" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="32" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35">
-    <cfRule type="cellIs" dxfId="27" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="26" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="27" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="28" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31">
-    <cfRule type="cellIs" dxfId="23" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="17" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="18" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32">
-    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="14" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+      <formula>"Complete"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E47">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"Todo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E5:E46">
+    <dataValidation type="list" sqref="E5:E47">
       <formula1>"Todo,In Progress,Blocked,Complete"</formula1>
     </dataValidation>
   </dataValidations>

--- a/backend/Backend-Daily-Tracker.xlsx
+++ b/backend/Backend-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="113">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -623,15 +623,18 @@
     <t>Added the chatbot backend for the restaurant platform. This includes new ChatSession and ChatMessage database models, and a chats module with a keyword-based bot that answers from real restaurant data (menu, offers, address, payment methods) in English and Japanese. It also has an optional AI fallback through Groq for questions the rules don’t cover, owner and platform-admin reply and close routes, and a visitor polling endpoint, with owner access limited to chats in their own tenant. I tested it end to end in Swagger: starting a chat, the bot replies, thread polling, and tenant isolation, which returned no chats for an owner from a different restaurant. The AI fallback first failed because Groq had retired the default model, so I updated the default model in the service. The server compiles cleanly, and the work is committed and pushed to the chatbot-backend branch.</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. feat(chats): add chat models
 2. feat(chats): add chats module
 3. fix(chats): update default groq model                              4. docs: added daily tracker spreadsheet                     </t>
   </si>
   <si>
     <t>Owner reply and takeover, closing a chat, platform-admin routes and the frontend widget are still to be tested or built. Pranav needs to be told about the shared-schema change before the PR is merged.</t>
+  </si>
+  <si>
+    <t>Connected the chat widget to the new chats API, so visitor messages now go to the server and get real replies from the restaurant’s menu, offers, address, and payment data. Added a single API file for the visitor, owner, and admin chat calls. Rewrote the chatbot hook so each conversation keeps its own server session, and the old built-in answers are used as a backup if the server or network fails. The widget now checks every 4 seconds for owner and admin replies, shows them in a labelled bubble, hides the quick-reply buttons once a human joins, and shows an “ended” notice with a “Start new chat” button when the chat is closed. Added the new translation keys to the English and Japanese message files. Adapted the AutoHub chat inbox into a shared component that refreshes every 5 seconds, and used it to build the new owner chats page and admin chats page. Owners can read, reply to, and end chats for their own restaurants, and admins can do the same across all restaurants. Added a Chats link to the owner and admin sidebars. Confirmed that the new files type-check, and the only TypeScript errors left are three that were already in the project.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. feat(chat-widget): connect widget to chats api                                 2. feat(chats): add owner and admin chat inbox                          3. docs: added daily tracker spreadsheet                     </t>
   </si>
 </sst>
 </file>
@@ -804,7 +807,63 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="52">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2444,27 +2503,39 @@
         <v>108</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>99</v>
       </c>
       <c r="G47" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H47" s="3" t="s">
+    </row>
+    <row r="48" spans="1:8" ht="303.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5">
+        <v>46323</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="6" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="16"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
+      <c r="E48" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H48" s="3"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
@@ -2512,161 +2583,175 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E29 E42:E44 E37:E39 E33:E34">
-    <cfRule type="cellIs" dxfId="43" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="49" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="50" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="51" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="52" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="cellIs" dxfId="39" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="45" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="46" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="47" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="48" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="35" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="41" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="42" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="43" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="44" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="31" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="37" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="38" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="39" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="40" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E36">
-    <cfRule type="cellIs" dxfId="27" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="33" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="34" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="35" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="36" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35">
-    <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="29" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="30" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="31" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="32" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31">
-    <cfRule type="cellIs" dxfId="19" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="21" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="22" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="23" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="24" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32">
-    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="17" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="18" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="19" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="20" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="13" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="14" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="15" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="16" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+      <formula>"Complete"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E48">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+      <formula>"Todo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E5:E47">
+    <dataValidation type="list" sqref="E5:E48">
       <formula1>"Todo,In Progress,Blocked,Complete"</formula1>
     </dataValidation>
   </dataValidations>

--- a/backend/Backend-Daily-Tracker.xlsx
+++ b/backend/Backend-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="115">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -634,7 +634,13 @@
     <t>Connected the chat widget to the new chats API, so visitor messages now go to the server and get real replies from the restaurant’s menu, offers, address, and payment data. Added a single API file for the visitor, owner, and admin chat calls. Rewrote the chatbot hook so each conversation keeps its own server session, and the old built-in answers are used as a backup if the server or network fails. The widget now checks every 4 seconds for owner and admin replies, shows them in a labelled bubble, hides the quick-reply buttons once a human joins, and shows an “ended” notice with a “Start new chat” button when the chat is closed. Added the new translation keys to the English and Japanese message files. Adapted the AutoHub chat inbox into a shared component that refreshes every 5 seconds, and used it to build the new owner chats page and admin chats page. Owners can read, reply to, and end chats for their own restaurants, and admins can do the same across all restaurants. Added a Chats link to the owner and admin sidebars. Confirmed that the new files type-check, and the only TypeScript errors left are three that were already in the project.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. feat(chat-widget): connect widget to chats api                                 2. feat(chats): add owner and admin chat inbox                          3. docs: added daily tracker spreadsheet                     </t>
+    <t>Tested the complete chatbot flow in the browser and on the API, and all tests passed. On the restaurant page, I checked that the widget gives real answers from the database for the menu, dish details, vegetarian options, offers, address with a map link, phone number, payment methods, delivery options, opening status, ratings, refund policy, and order-tracking questions. I also tested Japanese questions, the quick-reply buttons, and the fallback reply for unknown questions. On the owner side, I checked that a new visitor chat appears in the owner’s inbox, that the owner’s reply shows up in the visitor’s widget as a labelled message, and that the bot stops replying once a human joins. I also checked that ending a chat shows the “ended” notice and the “Start new chat” button, and that a logged-in customer’s name and email appear on the chat. I confirmed that another owner cannot see or reply to a chat from a different restaurant, and that the admin inbox shows all chats and admin replies appear as “Support team”. I tested the general chat on pages without a restaurant, including the nearest-restaurant search with location access, and confirmed the widget still replies from its built-in answers when the server is stopped or the AI is turned off. Finally, I checked the API in Swagger and confirmed it rejects bad ids, extra fields and fake sender names, blocks requests without a login, and rate-limits repeated chat starts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. docs: added daily tracker spreadsheet                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. feat(chat-widget): connect widget to chats api                                  2. feat(chats): add owner and admin chat inbox                          3. docs: added daily tracker spreadsheet                     </t>
   </si>
 </sst>
 </file>
@@ -807,7 +813,63 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="52">
+  <dxfs count="60">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2517,7 +2579,7 @@
     </row>
     <row r="48" spans="1:8" ht="303.60000000000002" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B48" s="5">
         <v>46323</v>
@@ -2533,19 +2595,31 @@
         <v>17</v>
       </c>
       <c r="G48" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8" ht="369.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>45</v>
+      </c>
+      <c r="B49" s="5">
+        <v>46324</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="16"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16"/>
+      <c r="E49" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H49" s="3"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="16"/>
@@ -2583,160 +2657,174 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E29 E42:E44 E37:E39 E33:E34">
-    <cfRule type="cellIs" dxfId="51" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="53" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="54" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="55" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="56" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="cellIs" dxfId="47" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="49" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="50" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="51" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="52" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="43" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="45" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="46" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="47" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="48" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="39" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="41" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="42" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="43" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="44" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E36">
-    <cfRule type="cellIs" dxfId="35" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="37" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="38" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="39" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="40" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35">
-    <cfRule type="cellIs" dxfId="31" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="33" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="34" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="35" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="36" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31">
-    <cfRule type="cellIs" dxfId="27" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="25" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="26" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="27" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="28" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32">
-    <cfRule type="cellIs" dxfId="23" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="21" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="22" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="23" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="24" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="cellIs" dxfId="19" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="17" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="18" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="19" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="20" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46">
-    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="13" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="14" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="15" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="16" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="10" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+      <formula>"Todo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+      <formula>"Complete"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E49">
     <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
@@ -2751,7 +2839,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E5:E48">
+    <dataValidation type="list" sqref="E5:E49">
       <formula1>"Todo,In Progress,Blocked,Complete"</formula1>
     </dataValidation>
   </dataValidations>

--- a/backend/Backend-Daily-Tracker.xlsx
+++ b/backend/Backend-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="116">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -614,9 +614,6 @@
     <t>Week 9</t>
   </si>
   <si>
-    <t>1. feat(owner): add error boundary, not-found page and orders error state                   2. docs: added daily tracker spreadsheet</t>
-  </si>
-  <si>
     <t>Added error handling to the owner dashboard. Built a shared QueryError card with a Try again button, an owner error.tsx error boundary, and a “Page not found” page for unknown owner URLs. On the Orders page Replaced the plain “Couldn’t load orders.” text with the new error card, and Replaced an as any with the existing getErrorMessage helper. Set up the project locally (dependencies, Docker database, Prisma schema and seed data) and moved the work onto a new branch from customer-redesign, because can’t merge to main right now. ran ESLint on the changed files with no errors, and then tested in the browser. An unknown owner URL showed the not-found card inside the dashboard. With the API stopped, Orders showed the error card, and Try again loaded the orders once the API was back</t>
   </si>
   <si>
@@ -641,6 +638,12 @@
   </si>
   <si>
     <t xml:space="preserve">1. feat(chat-widget): connect widget to chats api                                  2. feat(chats): add owner and admin chat inbox                          3. docs: added daily tracker spreadsheet                     </t>
+  </si>
+  <si>
+    <t>Had meeting with the frontend lead and went over all the recent changes and checked if any of those create any bugs anywhere else in the system. Also changed some parts in the system for better look and optimization as well as minimization. Tested the whole system's workflow as well</t>
+  </si>
+  <si>
+    <t>1. feat(owner): add error boundary, not-found page and orders error state                                2. docs: added daily tracker spreadsheet</t>
   </si>
 </sst>
 </file>
@@ -813,35 +816,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="60">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD1FAE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDBEAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F4F6"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="56">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2540,16 +2515,16 @@
         <v>105</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H46" s="3"/>
     </row>
@@ -2562,7 +2537,7 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>19</v>
@@ -2571,10 +2546,10 @@
         <v>99</v>
       </c>
       <c r="G47" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="303.60000000000002" x14ac:dyDescent="0.3">
@@ -2586,16 +2561,16 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H48" s="3"/>
     </row>
@@ -2608,7 +2583,7 @@
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>19</v>
@@ -2617,19 +2592,31 @@
         <v>17</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="16"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
+    <row r="50" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>46</v>
+      </c>
+      <c r="B50" s="5">
+        <v>46325</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H50" s="3"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="16"/>
@@ -2657,189 +2644,203 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E29 E42:E44 E37:E39 E33:E34">
-    <cfRule type="cellIs" dxfId="59" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="57" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="58" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="59" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="60" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="cellIs" dxfId="55" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="53" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="54" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="55" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="56" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="51" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="49" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="50" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="51" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="52" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="47" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="45" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="46" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="47" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="48" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E36">
-    <cfRule type="cellIs" dxfId="43" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="41" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="42" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="43" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="44" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35">
-    <cfRule type="cellIs" dxfId="39" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="37" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="38" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="39" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="40" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31">
-    <cfRule type="cellIs" dxfId="35" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="29" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="30" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="31" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="32" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32">
-    <cfRule type="cellIs" dxfId="31" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="25" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="26" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="27" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="28" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="cellIs" dxfId="27" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="21" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="22" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="23" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="24" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46">
-    <cfRule type="cellIs" dxfId="23" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="17" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="18" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="14" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E49">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+      <formula>"Complete"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E50">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"Todo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E5:E49">
+    <dataValidation type="list" sqref="E5:E50">
       <formula1>"Todo,In Progress,Blocked,Complete"</formula1>
     </dataValidation>
   </dataValidations>
